--- a/pensum/ok09/LOM_Ovingsark_Okonomistyring_kap09_Budsjett_NY.xlsx
+++ b/pensum/ok09/LOM_Ovingsark_Okonomistyring_kap09_Budsjett_NY.xlsx
@@ -1226,7 +1226,7 @@
         </is>
       </c>
       <c r="B8" s="13" t="n">
-        <v>0.48</v>
+        <v>0.625</v>
       </c>
       <c r="O8" s="6" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
         </is>
       </c>
       <c r="B10" s="12" t="n">
-        <v>480000</v>
+        <v>700000</v>
       </c>
     </row>
     <row r="11">
@@ -4114,7 +4114,7 @@
     <row r="89">
       <c r="A89" s="8" t="inlineStr">
         <is>
-          <t>Prøv dette: sett kredittiden i B5 til 44. Da er kontoen nøyaktig tom på det verste. Sett den til 54, som er det kundene faktisk brukte i 2026, og se hvor mange måneder som havner i minus.</t>
+          <t>Prøv dette: sett kredittiden i B5 til 44. Da er det bare 24 533 kroner igjen på det verste, og ved 45 går kontoen i minus. Sett den til 54, som er det kundene faktisk brukte i 2026, og se hvor mange måneder som havner i minus.</t>
         </is>
       </c>
     </row>
@@ -4265,10 +4265,10 @@
         </is>
       </c>
       <c r="B7" s="12" t="n">
-        <v>11440000</v>
+        <v>8240000</v>
       </c>
       <c r="C7" s="12" t="n">
-        <v>11650000</v>
+        <v>8390000</v>
       </c>
       <c r="D7" s="11">
         <f>B7-C7</f>
@@ -4299,10 +4299,10 @@
         </is>
       </c>
       <c r="B8" s="12" t="n">
-        <v>7260000</v>
+        <v>10460000</v>
       </c>
       <c r="C8" s="12" t="n">
-        <v>7400000</v>
+        <v>10660000</v>
       </c>
       <c r="D8" s="11">
         <f>B8-C8</f>
@@ -4799,11 +4799,11 @@
     </row>
     <row r="17">
       <c r="A17" s="18" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>44 dager</t>
+          <t>45 dager</t>
         </is>
       </c>
       <c r="C17" s="12" t="n">
@@ -4811,7 +4811,7 @@
       </c>
       <c r="E17" s="6" t="inlineStr">
         <is>
-          <t>Her er kontoen nøyaktig tom på det verste.</t>
+          <t>Her går kontoen i minus for første gang. Ved 44 dager er det 24 533 kroner igjen på det verste.</t>
         </is>
       </c>
     </row>
@@ -5052,7 +5052,7 @@
         </is>
       </c>
       <c r="B37" s="12" t="n">
-        <v>8802610</v>
+        <v>8817775</v>
       </c>
       <c r="C37" s="14">
         <f>B37</f>

--- a/pensum/ok09/LOM_Ovingsark_Okonomistyring_kap09_Budsjett_NY.xlsx
+++ b/pensum/ok09/LOM_Ovingsark_Okonomistyring_kap09_Budsjett_NY.xlsx
@@ -192,7 +192,7 @@
     <t xml:space="preserve">Tre scenarioer: hva kredittiden gjør med året, de fire tiltakene fra lærebokas liste, og kvartalet der budsjettet sprakk.</t>
   </si>
   <si>
-    <t xml:space="preserve">Tallene som ligger inne er budsjettet Nordlys Elektro AS har lagt for 2027, og budsjettkontrollen for 2026. Samme bedrift som i alle ti kapitlene i Bok 1.</t>
+    <t xml:space="preserve">Tallene som ligger inne er budsjettet Nordlys Elektro AS har lagt for 2027, og budsjettkontrollen for 2026. Samme bedrift som i alle ti kapitlene i Økonomistyring for LØM-emnet.</t>
   </si>
   <si>
     <t xml:space="preserve">Alle inndataceller er gule. Vil du bruke arket på din egen bedrift, bytter du dem ut — salgsprofilen, satsene, de inngående postene og forfallsmånedene.</t>
@@ -324,7 +324,7 @@
     <t xml:space="preserve">Bransjetall: NHO Elektro, Lønnsomhetsrapport 2025, gjengitt i Elektro 24-7 19.08.2026 (hentet 10.09.2026). De 809 er bedriftene i datagrunnlaget, ikke bransjen. NHO Elektro oppgir ikke svarprosent.</t>
   </si>
   <si>
-    <t xml:space="preserve">Nordlys Elektro AS er en konstruert casebedrift. Tallene henger sammen på tvers av alle ti kapitlene i Bok 1.</t>
+    <t xml:space="preserve">Nordlys Elektro AS er en konstruert casebedrift. Tallene henger sammen på tvers av alle ti kapitlene i Økonomistyring for LØM-emnet.</t>
   </si>
   <si>
     <t xml:space="preserve">Resultatbudsjett 2027</t>
@@ -483,7 +483,7 @@
     <t xml:space="preserve">Prøv dette: endre salget i en enkelt måned og se at driftsresultatet flytter seg. Gå så til arket Likviditet og endre kredittiden i B5 — der flytter kontobeholdningen seg uten at ett eneste tall her endrer seg.</t>
   </si>
   <si>
-    <t xml:space="preserve">Kilde: Bok 1 kap. 9.2 og 9.3. Tallene er budsjettet Nordlys Elektro AS har lagt for 2027.</t>
+    <t xml:space="preserve">Kilde: Økonomistyring for LØM-emnet kap. 9.2 og 9.3. Tallene er budsjettet Nordlys Elektro AS har lagt for 2027.</t>
   </si>
   <si>
     <t xml:space="preserve">Likviditetsbudsjett 2027</t>
@@ -774,7 +774,7 @@
     <t xml:space="preserve">Prøv dette: sett kredittiden i B5 til 44. Da er det bare 24 533 kroner igjen på det verste, og ved 45 går kontoen i minus. Sett den til 54, som er det kundene faktisk brukte i 2026, og se hvor mange måneder som havner i minus.</t>
   </si>
   <si>
-    <t xml:space="preserve">Kilde: Bok 1 kap. 9.4 til 9.6 om likviditetsbudsjettet, og 9.7 om tiltak. Forfallsreglene for merverdiavgift og arbeidsgiveravgift følger skattebetalingsloven og merverdiavgiftsloven (Lovdata).</t>
+    <t xml:space="preserve">Kilde: Økonomistyring for LØM-emnet kap. 9.4 til 9.6 om likviditetsbudsjettet, og 9.7 om tiltak. Forfallsreglene for merverdiavgift og arbeidsgiveravgift følger skattebetalingsloven og merverdiavgiftsloven (Lovdata).</t>
   </si>
   <si>
     <t xml:space="preserve">Budsjettkontroll 2026</t>
@@ -873,7 +873,7 @@
     <t xml:space="preserve">Avviksanalysen peker på stedet. Den gir ikke svaret. Det siste finner du bare ved å se på bilagene.</t>
   </si>
   <si>
-    <t xml:space="preserve">Kilde: Bok 1 kap. 9.8 om budsjettkontroll og avviksanalyse.</t>
+    <t xml:space="preserve">Kilde: Økonomistyring for LØM-emnet kap. 9.8 om budsjettkontroll og avviksanalyse.</t>
   </si>
   <si>
     <t xml:space="preserve">Tre scenarioer</t>
@@ -1068,7 +1068,7 @@
     <t xml:space="preserve">Var kredittiden synlig i regnskapet på forhånd?</t>
   </si>
   <si>
-    <t xml:space="preserve">Kilde: Bok 1 kap. 9.4 til 9.8. Kredittiden i 2026 er lest av balansen, slik kapittel 4 gjør det. Bransjetall: NHO Elektro, Lønnsomhetsrapport 2025, gjengitt i Elektro 24-7 19.08.2026 (hentet 10.09.2026). De 809 er bedriftene i datagrunnlaget, ikke bransjen. NHO Elektro oppgir ikke svarprosent.</t>
+    <t xml:space="preserve">Kilde: Økonomistyring for LØM-emnet kap. 9.4 til 9.8. Kredittiden i 2026 er lest av balansen, slik kapittel 4 gjør det. Bransjetall: NHO Elektro, Lønnsomhetsrapport 2025, gjengitt i Elektro 24-7 19.08.2026 (hentet 10.09.2026). De 809 er bedriftene i datagrunnlaget, ikke bransjen. NHO Elektro oppgir ikke svarprosent.</t>
   </si>
 </sst>
 </file>
